--- a/en/Manual/source/tab/connectors.xlsx
+++ b/en/Manual/source/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="63"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="60"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="517">
   <si>
     <t xml:space="preserve">This is a workbook with source tables of TGZ/TGS connector descriptions in English. Each sheet corresponds to one unique connector type. Since connectors are often repeated within TGZ (typically those on the control board), they are only listed once. I.e. E.g. IO connector 22pin weidmuller B2CF is used over and over again, so it is only listed here once as "X8_IO_22pin_B2CF"</t>
   </si>
@@ -295,6 +295,33 @@
     <t xml:space="preserve">#X3_DO_4pin_BCZ</t>
   </si>
   <si>
+    <t xml:space="preserve">#X4_ACIN_4pin_TGS560_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X4_TGS560_24V_5pin_BCZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X1_DC_6pin_TGS560_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR_RES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X5_RBR_3pin_TGS560_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIP-SWITCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#S1_TGS560_DIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X2_ACIN_7pin_2636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X6_TGS560_50_DCbus</t>
+  </si>
+  <si>
     <t xml:space="preserve">TGM</t>
   </si>
   <si>
@@ -422,6 +449,36 @@
   </si>
   <si>
     <t xml:space="preserve">BLZ 7.62HP/03/180LR SN BK BX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BVZ 7.62HP/04/180F SN BK BX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BVZ 7.62HP/06/180F SN BK BX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLZ 7.62HP/03/180F SN BK BX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS03-254-04BE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same Sky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCZ 3.81/05/180F SN OR BX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2636-1107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kabelové oko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLF 5.00HC/06/180F SN OR BX           </t>
   </si>
   <si>
     <t xml:space="preserve">pin #</t>
@@ -1484,7 +1541,7 @@
     <t xml:space="preserve">TERM1</t>
   </si>
   <si>
-    <t xml:space="preserve">Vstup termokontaktu ext. br. rez.</t>
+    <t xml:space="preserve">Thermistor input 1 (positive)</t>
   </si>
   <si>
     <t xml:space="preserve">16~28</t>
@@ -1493,10 +1550,10 @@
     <t xml:space="preserve">TERM2</t>
   </si>
   <si>
-    <t xml:space="preserve">+24V napájení řízení</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nezapojeno</t>
+    <t xml:space="preserve">Thermistor input 2 (negative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+24V logic power</t>
   </si>
   <si>
     <t xml:space="preserve">+140 ~ +600V</t>
@@ -1590,9 +1647,6 @@
   </si>
   <si>
     <t xml:space="preserve">Green LED</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">permanently on</t>
@@ -1935,8 +1989,9 @@
           <cell r="A2" t="str">
             <v>#X1_24V_5pin_Microlock</v>
           </cell>
-        </row>
-        <row r="2">
+          <cell r="B2">
+            <v>5055700501</v>
+          </cell>
           <cell r="C2" t="str">
             <v>Molex</v>
           </cell>
@@ -1948,8 +2003,9 @@
           <cell r="A3" t="str">
             <v>#X8_IO_22pin_B2CF</v>
           </cell>
-        </row>
-        <row r="3">
+          <cell r="B3" t="str">
+            <v>B2CF 3.50/22/180 SN OR BX</v>
+          </cell>
           <cell r="C3" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -1961,8 +2017,9 @@
           <cell r="A4" t="str">
             <v>#X10_CAN_4pin_B2CF</v>
           </cell>
-        </row>
-        <row r="4">
+          <cell r="B4" t="str">
+            <v>B2CF 3.50/04/180 SN OR BX</v>
+          </cell>
           <cell r="C4" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -1974,8 +2031,9 @@
           <cell r="A5" t="str">
             <v>#X6_FB1_8pin_B2CF</v>
           </cell>
-        </row>
-        <row r="5">
+          <cell r="B5" t="str">
+            <v>B2CF 3.50/08/180 SN OR BX</v>
+          </cell>
           <cell r="C5" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -1987,8 +2045,9 @@
           <cell r="A6" t="str">
             <v>#X7_FB2_8pin_B2CF</v>
           </cell>
-        </row>
-        <row r="6">
+          <cell r="B6" t="str">
+            <v>B2CF 3.50/08/180 SN OR BX</v>
+          </cell>
           <cell r="C6" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2000,8 +2059,9 @@
           <cell r="A7" t="str">
             <v>#X5_FBE_12pin_B2CF</v>
           </cell>
-        </row>
-        <row r="7">
+          <cell r="B7" t="str">
+            <v>B2CF 3.50/12/180 SN OR BX</v>
+          </cell>
           <cell r="C7" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2013,8 +2073,9 @@
           <cell r="A8" t="str">
             <v>#X1_24V_5pin_BCZ</v>
           </cell>
-        </row>
-        <row r="8">
+          <cell r="B8" t="str">
+            <v>BCZ 3.81/05/180 SN OR BX</v>
+          </cell>
           <cell r="C8" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2026,8 +2087,9 @@
           <cell r="A9" t="str">
             <v>#X3_M1_6pin_BLZP</v>
           </cell>
-        </row>
-        <row r="9">
+          <cell r="B9" t="str">
+            <v>BLZP 5.08HC/06/180 SN OR BX</v>
+          </cell>
           <cell r="C9" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2039,8 +2101,9 @@
           <cell r="A10" t="str">
             <v>#X4_M2_6pin_BLZP</v>
           </cell>
-        </row>
-        <row r="10">
+          <cell r="B10" t="str">
+            <v>BLZP 5.08HC/06/180 SN OR BX</v>
+          </cell>
           <cell r="C10" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2052,8 +2115,9 @@
           <cell r="A11" t="str">
             <v>#X2_48_DC_1778065</v>
           </cell>
-        </row>
-        <row r="11">
+          <cell r="B11" t="str">
+            <v>PC 5/ 2-STCL1-7,62</v>
+          </cell>
           <cell r="C11" t="str">
             <v>Phoenix Contact</v>
           </cell>
@@ -2065,8 +2129,9 @@
           <cell r="A12" t="str">
             <v>#X4_M1_6pin_SLS</v>
           </cell>
-        </row>
-        <row r="12">
+          <cell r="B12" t="str">
+            <v>SLS 5.08/06/180FI SN OR BX</v>
+          </cell>
           <cell r="C12" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2078,8 +2143,9 @@
           <cell r="A13" t="str">
             <v>#X2_PWR_10pin_BLZP</v>
           </cell>
-        </row>
-        <row r="13">
+          <cell r="B13" t="str">
+            <v>BLZP 5.08HC/10/180 SN OR BX</v>
+          </cell>
           <cell r="C13" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2091,8 +2157,9 @@
           <cell r="A14" t="str">
             <v>#X4_M1_6pin_BLF</v>
           </cell>
-        </row>
-        <row r="14">
+          <cell r="B14" t="str">
+            <v>BLF 7.62HP/06/180F</v>
+          </cell>
           <cell r="C14" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2104,8 +2171,9 @@
           <cell r="A15" t="str">
             <v>#X2_PWR_12pin_BLZ</v>
           </cell>
-        </row>
-        <row r="15">
+          <cell r="B15" t="str">
+            <v>BLZ 7.62HP/12/180F</v>
+          </cell>
           <cell r="C15" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2117,8 +2185,9 @@
           <cell r="A16" t="str">
             <v>#X3_M1_4pin_wago_2636</v>
           </cell>
-        </row>
-        <row r="16">
+          <cell r="B16" t="str">
+            <v>PC 5/ 2-STCL1-7,62</v>
+          </cell>
           <cell r="C16" t="str">
             <v>Phoenix Contact</v>
           </cell>
@@ -2130,8 +2199,9 @@
           <cell r="A17" t="str">
             <v>#X4_M2_4pin_wago_2636</v>
           </cell>
-        </row>
-        <row r="17">
+          <cell r="B17" t="str">
+            <v>PC 5/ 2-STCL1-7,62</v>
+          </cell>
           <cell r="C17" t="str">
             <v>Phoenix Contact</v>
           </cell>
@@ -2143,8 +2213,9 @@
           <cell r="A18" t="str">
             <v>#X2_D560DCbus</v>
           </cell>
-        </row>
-        <row r="18">
+          <cell r="B18" t="str">
+            <v>Svorky M8</v>
+          </cell>
           <cell r="C18" t="str">
             <v>-</v>
           </cell>
@@ -2156,8 +2227,9 @@
           <cell r="A19" t="str">
             <v>#X14_BR1_4pin_LSF</v>
           </cell>
-        </row>
-        <row r="19">
+          <cell r="B19" t="str">
+            <v>Push-in</v>
+          </cell>
           <cell r="C19" t="str">
             <v>-</v>
           </cell>
@@ -2169,8 +2241,9 @@
           <cell r="A20" t="str">
             <v>#X15_BR2_4pin_LSF</v>
           </cell>
-        </row>
-        <row r="20">
+          <cell r="B20" t="str">
+            <v>Push-in</v>
+          </cell>
           <cell r="C20" t="str">
             <v>-</v>
           </cell>
@@ -2182,8 +2255,9 @@
           <cell r="A21" t="str">
             <v>#X1_ACIN_PC5</v>
           </cell>
-        </row>
-        <row r="21">
+          <cell r="B21" t="str">
+            <v>PC 5/ 8-STCL1-7,62</v>
+          </cell>
           <cell r="C21" t="str">
             <v>Phoenix Contact</v>
           </cell>
@@ -2195,8 +2269,9 @@
           <cell r="A22" t="str">
             <v>#X2_DC_8pin_PC5</v>
           </cell>
-        </row>
-        <row r="22">
+          <cell r="B22" t="str">
+            <v>PC 5/ 8-STCL1-7,62</v>
+          </cell>
           <cell r="C22" t="str">
             <v>Phoenix Contact</v>
           </cell>
@@ -2208,8 +2283,9 @@
           <cell r="A23" t="str">
             <v>#X3_DO_4pin_BCZ</v>
           </cell>
-        </row>
-        <row r="23">
+          <cell r="B23" t="str">
+            <v>BCZ 3.81/04/180 SN BK BX</v>
+          </cell>
           <cell r="C23" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2221,8 +2297,9 @@
           <cell r="A24" t="str">
             <v>#X3_24V_BLF_2_5</v>
           </cell>
-        </row>
-        <row r="24">
+          <cell r="B24" t="str">
+            <v>BLF 2.50/04/180 SN OR BX</v>
+          </cell>
           <cell r="C24" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2234,8 +2311,9 @@
           <cell r="A25" t="str">
             <v>#X10_CAN_4pin_B2CF</v>
           </cell>
-        </row>
-        <row r="25">
+          <cell r="B25" t="str">
+            <v>BCZ 3.81/04/180 SN OR BX</v>
+          </cell>
           <cell r="C25" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2247,8 +2325,9 @@
           <cell r="A26" t="str">
             <v>#X5_DI_10pin_B2CF</v>
           </cell>
-        </row>
-        <row r="26">
+          <cell r="B26" t="str">
+            <v>B2CF 3.50/10/180 SN OR BX</v>
+          </cell>
           <cell r="C26" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2260,8 +2339,9 @@
           <cell r="A27" t="str">
             <v>#X10_DO_10pin_B2CF</v>
           </cell>
-        </row>
-        <row r="27">
+          <cell r="B27" t="str">
+            <v>B2CF 3.50/10/180 SN OR BX</v>
+          </cell>
           <cell r="C27" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2273,8 +2353,9 @@
           <cell r="A28" t="str">
             <v>#X1_24V_5pin_BCZ_TGM</v>
           </cell>
-        </row>
-        <row r="28">
+          <cell r="B28" t="str">
+            <v>BCZ 3.81/05/180 SN OR BX</v>
+          </cell>
           <cell r="C28" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2286,8 +2367,9 @@
           <cell r="A29" t="str">
             <v>#X2_320_DC_1778078</v>
           </cell>
-        </row>
-        <row r="29">
+          <cell r="B29" t="str">
+            <v>PC 5/ 3-STCL1-7,62</v>
+          </cell>
           <cell r="C29" t="str">
             <v>Phoenix Contact</v>
           </cell>
@@ -2299,8 +2381,9 @@
           <cell r="A30" t="str">
             <v>#X6_FB1_8pin_B2CF_TGM</v>
           </cell>
-        </row>
-        <row r="30">
+          <cell r="B30" t="str">
+            <v>BCZ 3.81/08/180 SN OR BX</v>
+          </cell>
           <cell r="C30" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2312,8 +2395,9 @@
           <cell r="A31" t="str">
             <v>#X7_FB2_8pin_B2CF_TGM</v>
           </cell>
-        </row>
-        <row r="31">
+          <cell r="B31" t="str">
+            <v>BCZ 3.81/08/180 SN OR BX</v>
+          </cell>
           <cell r="C31" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2325,8 +2409,9 @@
           <cell r="A32" t="str">
             <v>#X5_FBE_12pin_B2CF_TGM</v>
           </cell>
-        </row>
-        <row r="32">
+          <cell r="B32" t="str">
+            <v>BCZ 3.81/12/180 SN OR BX</v>
+          </cell>
           <cell r="C32" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2338,8 +2423,9 @@
           <cell r="A33" t="str">
             <v>jen šrouby</v>
           </cell>
-        </row>
-        <row r="33">
+          <cell r="B33" t="str">
+            <v>kabelové oko</v>
+          </cell>
           <cell r="C33" t="str">
             <v>-</v>
           </cell>
@@ -2351,8 +2437,9 @@
           <cell r="A34" t="str">
             <v>#X3_M1_3pin_pressfit</v>
           </cell>
-        </row>
-        <row r="34">
+          <cell r="B34" t="str">
+            <v>kabelové oko</v>
+          </cell>
           <cell r="C34" t="str">
             <v>-</v>
           </cell>
@@ -2364,8 +2451,9 @@
           <cell r="A35" t="str">
             <v>#X3_DCbus_2pin_pressfit</v>
           </cell>
-        </row>
-        <row r="35">
+          <cell r="B35" t="str">
+            <v>kabelové oko</v>
+          </cell>
           <cell r="C35" t="str">
             <v>-</v>
           </cell>
@@ -2377,8 +2465,9 @@
           <cell r="A36" t="str">
             <v>#X3_M1_4pin_wago_2626</v>
           </cell>
-        </row>
-        <row r="36">
+          <cell r="B36" t="str">
+            <v>Push-in</v>
+          </cell>
           <cell r="C36" t="str">
             <v>-</v>
           </cell>
@@ -2390,8 +2479,9 @@
           <cell r="A37" t="str">
             <v>#X4_M2_4pin_wago_2626</v>
           </cell>
-        </row>
-        <row r="37">
+          <cell r="B37" t="str">
+            <v>Push-in</v>
+          </cell>
           <cell r="C37" t="str">
             <v>-</v>
           </cell>
@@ -2403,8 +2493,9 @@
           <cell r="A38" t="str">
             <v>#X2_DCbus_3pin_wago_2636</v>
           </cell>
-        </row>
-        <row r="38">
+          <cell r="B38" t="str">
+            <v>Push-in</v>
+          </cell>
           <cell r="C38" t="str">
             <v>-</v>
           </cell>
@@ -2416,8 +2507,9 @@
           <cell r="A39" t="str">
             <v>#X3_M1_6pin_BLZ__7_62</v>
           </cell>
-        </row>
-        <row r="39">
+          <cell r="B39" t="str">
+            <v>BLZ 7.62HP/06/180LR SN BK BX</v>
+          </cell>
           <cell r="C39" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2429,8 +2521,9 @@
           <cell r="A40" t="str">
             <v>#X4_M2_6pin_BLZ__7_62</v>
           </cell>
-        </row>
-        <row r="40">
+          <cell r="B40" t="str">
+            <v>BLZ 7.62HP/06/180LR SN BK BX</v>
+          </cell>
           <cell r="C40" t="str">
             <v>Weidmüller</v>
           </cell>
@@ -2442,13 +2535,126 @@
           <cell r="A41" t="str">
             <v>#X2_560_DC_3pin_BLZ__7_62</v>
           </cell>
-        </row>
-        <row r="41">
+          <cell r="B41" t="str">
+            <v>BLZ 7.62HP/03/180LR SN BK BX</v>
+          </cell>
           <cell r="C41" t="str">
             <v>Weidmüller</v>
           </cell>
           <cell r="D41">
             <v>3</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42" t="str">
+            <v>#X4_ACIN_4pin_TGS560_25</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>BVZ 7.62HP/04/180F SN BK BX</v>
+          </cell>
+          <cell r="C42" t="str">
+            <v>Weidmüller</v>
+          </cell>
+          <cell r="D42">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43" t="str">
+            <v>#X1_DC_6pin_TGS560_25</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>BVZ 7.62HP/06/180F SN BK BX</v>
+          </cell>
+          <cell r="C43" t="str">
+            <v>Weidmüller</v>
+          </cell>
+          <cell r="D43">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44" t="str">
+            <v>#X5_RBR_3pin_TGS560_25</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>BLZ 7.62HP/03/180F SN BK BX</v>
+          </cell>
+          <cell r="C44" t="str">
+            <v>Weidmüller</v>
+          </cell>
+          <cell r="D44">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45" t="str">
+            <v>#S1_TGS560_DIP</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>DS03-254-04BE</v>
+          </cell>
+          <cell r="C45" t="str">
+            <v>Same Sky</v>
+          </cell>
+          <cell r="D45">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46" t="str">
+            <v>#X4_TGS560_24V_5pin_BCZ</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>BCZ 3.81/05/180F SN OR BX</v>
+          </cell>
+          <cell r="C46" t="str">
+            <v>Weidmüller</v>
+          </cell>
+          <cell r="D46">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47" t="str">
+            <v>#X2_ACIN_7pin_2636</v>
+          </cell>
+          <cell r="B47" t="str">
+            <v>2636-1107</v>
+          </cell>
+          <cell r="C47" t="str">
+            <v>Wago</v>
+          </cell>
+          <cell r="D47">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>#X6_TGS560_50_DCbus</v>
+          </cell>
+          <cell r="B48" t="str">
+            <v>kabelové oko</v>
+          </cell>
+          <cell r="C48" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="D48">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49" t="str">
+            <v>#XBR_BR_6pin_BLF</v>
+          </cell>
+          <cell r="B49" t="str">
+            <v>BLF 5.00HC/06/180F SN OR BX          </v>
+          </cell>
+          <cell r="C49" t="str">
+            <v>Weidmüller</v>
+          </cell>
+          <cell r="D49">
+            <v>6</v>
           </cell>
         </row>
         <row r="59">
@@ -2715,7 +2921,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K175"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr defaultColWidth="12.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.82"/>
@@ -7102,25 +7308,21 @@
         <v>64</v>
       </c>
       <c r="I156" s="6" t="str">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H156, conns!$A$2:$A$500, 0))</f>
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H156, [1]conns!$A$2:$A$501, 0))</f>
         <v>PC 5/ 8-STCL1-7,62 </v>
       </c>
       <c r="J156" s="6" t="str">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H156, conns!$A$2:$A$500, 0))</f>
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H156, [1]conns!$A$2:$A$501, 0))</f>
         <v>Phoenix Contact</v>
       </c>
       <c r="K156" s="6" t="n">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H156, conns!$A$2:$A$500, 0))</f>
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H156, [1]conns!$A$2:$A$501, 0))</f>
         <v>8</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
@@ -7131,25 +7333,21 @@
         <v>66</v>
       </c>
       <c r="I157" s="6" t="str">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H157, conns!$A$2:$A$500, 0))</f>
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H157, [1]conns!$A$2:$A$501, 0))</f>
         <v>PC 5/ 8-STCL1-7,62 </v>
       </c>
       <c r="J157" s="6" t="str">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H157, conns!$A$2:$A$500, 0))</f>
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H157, [1]conns!$A$2:$A$501, 0))</f>
         <v>Phoenix Contact</v>
       </c>
       <c r="K157" s="6" t="n">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H157, conns!$A$2:$A$500, 0))</f>
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H157, [1]conns!$A$2:$A$501, 0))</f>
         <v>8</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
@@ -7160,25 +7358,21 @@
         <v>68</v>
       </c>
       <c r="I158" s="6" t="str">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H158, conns!$A$2:$A$500, 0))</f>
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H158, [1]conns!$A$2:$A$501, 0))</f>
         <v>BCZ 3.81/04/180 SN BK BX </v>
       </c>
       <c r="J158" s="6" t="str">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H158, conns!$A$2:$A$500, 0))</f>
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H158, [1]conns!$A$2:$A$501, 0))</f>
         <v>Weidmüller</v>
       </c>
       <c r="K158" s="6" t="n">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H158, conns!$A$2:$A$500, 0))</f>
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H158, [1]conns!$A$2:$A$501, 0))</f>
         <v>4</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B159" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
       <c r="D159" s="4" t="n">
         <v>560</v>
       </c>
@@ -7191,288 +7385,284 @@
       <c r="G159" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I159" s="6" t="e">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H159, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J159" s="6" t="e">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H159, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K159" s="6" t="e">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H159, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
+      <c r="H159" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I159" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H159, [1]conns!$A$2:$A$501, 0))</f>
+        <v>BVZ 7.62HP/04/180F SN BK BX </v>
+      </c>
+      <c r="J159" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H159, [1]conns!$A$2:$A$501, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K159" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H159, [1]conns!$A$2:$A$501, 0))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
       <c r="G160" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I160" s="6" t="e">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H160, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J160" s="6" t="e">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H160, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K160" s="6" t="e">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H160, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
+        <v>16</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I160" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H160, [1]conns!$A$2:$A$501, 0))</f>
+        <v>BCZ 3.81/05/180F SN OR BX </v>
+      </c>
+      <c r="J160" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H160, [1]conns!$A$2:$A$501, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K160" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H160, [1]conns!$A$2:$A$501, 0))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
       <c r="G161" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I161" s="6" t="e">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H161, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J161" s="6" t="e">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H161, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K161" s="6" t="e">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H161, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
+        <v>65</v>
+      </c>
+      <c r="H161" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I161" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H161, [1]conns!$A$2:$A$501, 0))</f>
+        <v>BVZ 7.62HP/06/180F SN BK BX </v>
+      </c>
+      <c r="J161" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H161, [1]conns!$A$2:$A$501, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K161" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H161, [1]conns!$A$2:$A$501, 0))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D162" s="4" t="n">
-        <v>560</v>
-      </c>
-      <c r="E162" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F162" s="4" t="n">
-        <v>100</v>
-      </c>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4"/>
       <c r="G162" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I162" s="6" t="e">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H162, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J162" s="6" t="e">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H162, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K162" s="6" t="e">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H162, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
+        <v>72</v>
+      </c>
+      <c r="H162" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I162" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H162, [1]conns!$A$2:$A$501, 0))</f>
+        <v>BLZ 7.62HP/03/180F SN BK BX </v>
+      </c>
+      <c r="J162" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H162, [1]conns!$A$2:$A$501, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K162" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H162, [1]conns!$A$2:$A$501, 0))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B163" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
       <c r="G163" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I163" s="6" t="e">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H163, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J163" s="6" t="e">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H163, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K163" s="6" t="e">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H163, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
+        <v>74</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I163" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H163, [1]conns!$A$2:$A$501, 0))</f>
+        <v>DS03-254-04BE </v>
+      </c>
+      <c r="J163" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H163, [1]conns!$A$2:$A$501, 0))</f>
+        <v>Same Sky</v>
+      </c>
+      <c r="K163" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H163, [1]conns!$A$2:$A$501, 0))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
       <c r="G164" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I164" s="6" t="e">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H164, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J164" s="6" t="e">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H164, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K164" s="6" t="e">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H164, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
+      <c r="H164" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I164" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H164, [1]conns!$A$2:$A$501, 0))</f>
+        <v>BCZ 3.81/04/180 SN BK BX </v>
+      </c>
+      <c r="J164" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H164, [1]conns!$A$2:$A$501, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K164" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H164, [1]conns!$A$2:$A$501, 0))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C165" s="3" t="s">
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="4" t="n">
+        <v>560</v>
+      </c>
+      <c r="E165" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I165" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H165, [1]conns!$A$2:$A$501, 0))</f>
+        <v>2636-1107</v>
+      </c>
+      <c r="J165" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H165, [1]conns!$A$2:$A$501, 0))</f>
+        <v>Wago</v>
+      </c>
+      <c r="K165" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H165, [1]conns!$A$2:$A$501, 0))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4"/>
+      <c r="G166" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I166" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H166, [1]conns!$A$2:$A$501, 0))</f>
+        <v>kabelové oko</v>
+      </c>
+      <c r="J166" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H166, [1]conns!$A$2:$A$501, 0))</f>
+        <v>-</v>
+      </c>
+      <c r="K166" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H166, [1]conns!$A$2:$A$501, 0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="4"/>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4"/>
+      <c r="G167" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H167" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I167" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H167, [1]conns!$A$2:$A$501, 0))</f>
+        <v>BCZ 3.81/04/180 SN BK BX </v>
+      </c>
+      <c r="J167" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H167, [1]conns!$A$2:$A$501, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K167" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H167, [1]conns!$A$2:$A$501, 0))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4"/>
+      <c r="G168" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H168" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D165" s="3"/>
-      <c r="E165" s="3"/>
-      <c r="F165" s="3"/>
-      <c r="G165" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H165" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I165" s="6" t="str">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H165, conns!$A$2:$A$500, 0))</f>
-        <v>BLF 2.50/04/180 SN OR BX </v>
-      </c>
-      <c r="J165" s="6" t="str">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H165, conns!$A$2:$A$500, 0))</f>
+      <c r="I168" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H168, [1]conns!$A$2:$A$501, 0))</f>
+        <v>BCZ 3.81/05/180F SN OR BX </v>
+      </c>
+      <c r="J168" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H168, [1]conns!$A$2:$A$501, 0))</f>
         <v>Weidmüller</v>
       </c>
-      <c r="K165" s="6" t="n">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H165, conns!$A$2:$A$500, 0))</f>
+      <c r="K168" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H168, [1]conns!$A$2:$A$501, 0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4"/>
+      <c r="G169" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I169" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$B$2:$B$501, MATCH(H169, [1]conns!$A$2:$A$501, 0))</f>
+        <v>DS03-254-04BE </v>
+      </c>
+      <c r="J169" s="6" t="str">
+        <f aca="false">INDEX([1]conns!$C$2:$C$501, MATCH(H169, [1]conns!$A$2:$A$501, 0))</f>
+        <v>Same Sky</v>
+      </c>
+      <c r="K169" s="6" t="n">
+        <f aca="false">INDEX([1]conns!$D$2:$D$501, MATCH(H169, [1]conns!$A$2:$A$501, 0))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="4"/>
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
-      <c r="F166" s="3"/>
-      <c r="G166" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H166" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I166" s="6" t="str">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H166, conns!$A$2:$A$500, 0))</f>
-        <v>B2CF 3.50/04/180 SN OR BX </v>
-      </c>
-      <c r="J166" s="6" t="str">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H166, conns!$A$2:$A$500, 0))</f>
-        <v>Weidmüller</v>
-      </c>
-      <c r="K166" s="6" t="n">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H166, conns!$A$2:$A$500, 0))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="4"/>
-      <c r="C167" s="3"/>
-      <c r="D167" s="3"/>
-      <c r="E167" s="3"/>
-      <c r="F167" s="3"/>
-      <c r="G167" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H167" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I167" s="6" t="e">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H167, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J167" s="6" t="e">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H167, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K167" s="6" t="e">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H167, conns!$A$2:$A$500, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="4"/>
-      <c r="C168" s="3"/>
-      <c r="D168" s="3"/>
-      <c r="E168" s="3"/>
-      <c r="F168" s="3"/>
-      <c r="G168" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H168" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I168" s="6" t="str">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H168, conns!$A$2:$A$500, 0))</f>
-        <v>B2CF 3.50/10/180 SN OR BX </v>
-      </c>
-      <c r="J168" s="6" t="str">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H168, conns!$A$2:$A$500, 0))</f>
-        <v>Weidmüller</v>
-      </c>
-      <c r="K168" s="6" t="n">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H168, conns!$A$2:$A$500, 0))</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="4"/>
-      <c r="C169" s="3"/>
-      <c r="D169" s="3"/>
-      <c r="E169" s="3"/>
-      <c r="F169" s="3"/>
-      <c r="G169" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H169" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I169" s="6" t="str">
-        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H169, conns!$A$2:$A$500, 0))</f>
-        <v>B2CF 3.50/10/180 SN OR BX </v>
-      </c>
-      <c r="J169" s="6" t="str">
-        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H169, conns!$A$2:$A$500, 0))</f>
-        <v>Weidmüller</v>
-      </c>
-      <c r="K169" s="6" t="n">
-        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H169, conns!$A$2:$A$500, 0))</f>
-        <v>10</v>
-      </c>
-    </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="4"/>
+      <c r="B170" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="C170" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -7481,11 +7671,11 @@
         <v>16</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I170" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H170, conns!$A$2:$A$500, 0))</f>
-        <v>BCZ 3.81/05/180 SN OR BX </v>
+        <v>BLF 2.50/04/180 SN OR BX </v>
       </c>
       <c r="J170" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H170, conns!$A$2:$A$500, 0))</f>
@@ -7493,12 +7683,12 @@
       </c>
       <c r="K170" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H170, conns!$A$2:$A$500, 0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B171" s="4"/>
-      <c r="C171" s="4"/>
+      <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
@@ -7523,44 +7713,44 @@
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B172" s="4"/>
-      <c r="C172" s="4"/>
+      <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H172" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I172" s="6" t="str">
+        <v>81</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I172" s="6" t="e">
         <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H172, conns!$A$2:$A$500, 0))</f>
-        <v>B2CF 3.50/22/180 SN OR BX</v>
-      </c>
-      <c r="J172" s="6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="J172" s="6" t="e">
         <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H172, conns!$A$2:$A$500, 0))</f>
-        <v>Weidmüller</v>
-      </c>
-      <c r="K172" s="6" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="K172" s="6" t="e">
         <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H172, conns!$A$2:$A$500, 0))</f>
-        <v>22</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
+      <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="1" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I173" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H173, conns!$A$2:$A$500, 0))</f>
-        <v>BCZ 3.81/08/180 SN OR BX </v>
+        <v>B2CF 3.50/10/180 SN OR BX </v>
       </c>
       <c r="J173" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H173, conns!$A$2:$A$500, 0))</f>
@@ -7568,24 +7758,24 @@
       </c>
       <c r="K173" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H173, conns!$A$2:$A$500, 0))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
+      <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I174" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H174, conns!$A$2:$A$500, 0))</f>
-        <v>BCZ 3.81/08/180 SN OR BX </v>
+        <v>B2CF 3.50/10/180 SN OR BX </v>
       </c>
       <c r="J174" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H174, conns!$A$2:$A$500, 0))</f>
@@ -7593,24 +7783,26 @@
       </c>
       <c r="K174" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H174, conns!$A$2:$A$500, 0))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B175" s="4"/>
-      <c r="C175" s="4"/>
+      <c r="C175" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I175" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H175, conns!$A$2:$A$500, 0))</f>
-        <v>BCZ 3.81/12/180 SN OR BX </v>
+        <v>BCZ 3.81/05/180 SN OR BX </v>
       </c>
       <c r="J175" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H175, conns!$A$2:$A$500, 0))</f>
@@ -7618,6 +7810,131 @@
       </c>
       <c r="K175" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H175, conns!$A$2:$A$500, 0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B176" s="4"/>
+      <c r="C176" s="4"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
+      <c r="F176" s="3"/>
+      <c r="G176" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I176" s="6" t="str">
+        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H176, conns!$A$2:$A$500, 0))</f>
+        <v>B2CF 3.50/04/180 SN OR BX </v>
+      </c>
+      <c r="J176" s="6" t="str">
+        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H176, conns!$A$2:$A$500, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K176" s="6" t="n">
+        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H176, conns!$A$2:$A$500, 0))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B177" s="4"/>
+      <c r="C177" s="4"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="3"/>
+      <c r="F177" s="3"/>
+      <c r="G177" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H177" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I177" s="6" t="str">
+        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H177, conns!$A$2:$A$500, 0))</f>
+        <v>B2CF 3.50/22/180 SN OR BX</v>
+      </c>
+      <c r="J177" s="6" t="str">
+        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H177, conns!$A$2:$A$500, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K177" s="6" t="n">
+        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H177, conns!$A$2:$A$500, 0))</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B178" s="4"/>
+      <c r="C178" s="4"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+      <c r="F178" s="3"/>
+      <c r="G178" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H178" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I178" s="6" t="str">
+        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H178, conns!$A$2:$A$500, 0))</f>
+        <v>BCZ 3.81/08/180 SN OR BX </v>
+      </c>
+      <c r="J178" s="6" t="str">
+        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H178, conns!$A$2:$A$500, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K178" s="6" t="n">
+        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H178, conns!$A$2:$A$500, 0))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B179" s="4"/>
+      <c r="C179" s="4"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H179" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I179" s="6" t="str">
+        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H179, conns!$A$2:$A$500, 0))</f>
+        <v>BCZ 3.81/08/180 SN OR BX </v>
+      </c>
+      <c r="J179" s="6" t="str">
+        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H179, conns!$A$2:$A$500, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K179" s="6" t="n">
+        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H179, conns!$A$2:$A$500, 0))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B180" s="4"/>
+      <c r="C180" s="4"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H180" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I180" s="6" t="str">
+        <f aca="false">INDEX(conns!$B$2:$B$500, MATCH(H180, conns!$A$2:$A$500, 0))</f>
+        <v>BCZ 3.81/12/180 SN OR BX </v>
+      </c>
+      <c r="J180" s="6" t="str">
+        <f aca="false">INDEX(conns!$C$2:$C$500, MATCH(H180, conns!$A$2:$A$500, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K180" s="6" t="n">
+        <f aca="false">INDEX(conns!$D$2:$D$500, MATCH(H180, conns!$A$2:$A$500, 0))</f>
         <v>12</v>
       </c>
     </row>
@@ -7667,20 +7984,20 @@
     <mergeCell ref="F136:F144"/>
     <mergeCell ref="E145:E155"/>
     <mergeCell ref="F145:F155"/>
-    <mergeCell ref="B156:B164"/>
-    <mergeCell ref="C156:C164"/>
+    <mergeCell ref="B156:B169"/>
+    <mergeCell ref="C156:C169"/>
     <mergeCell ref="D156:D158"/>
     <mergeCell ref="E156:E158"/>
     <mergeCell ref="F156:F158"/>
-    <mergeCell ref="D159:D161"/>
-    <mergeCell ref="E159:E161"/>
-    <mergeCell ref="F159:F161"/>
-    <mergeCell ref="D162:D164"/>
-    <mergeCell ref="E162:E164"/>
-    <mergeCell ref="F162:F164"/>
-    <mergeCell ref="B165:B175"/>
-    <mergeCell ref="C165:F169"/>
-    <mergeCell ref="C170:F175"/>
+    <mergeCell ref="D159:D164"/>
+    <mergeCell ref="E159:E164"/>
+    <mergeCell ref="F159:F164"/>
+    <mergeCell ref="D165:D169"/>
+    <mergeCell ref="E165:E169"/>
+    <mergeCell ref="F165:F169"/>
+    <mergeCell ref="B170:B180"/>
+    <mergeCell ref="C170:F174"/>
+    <mergeCell ref="C175:F180"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H9" location="X1_24V_5pin_Microlock!A1" display="#X1_24V_5pin_Microlock"/>
@@ -7827,17 +8144,28 @@
     <hyperlink ref="H156" location="X1_ACIN_PC5!A1" display="#X1_ACIN_PC5"/>
     <hyperlink ref="H157" location="X2_DC_8pin_PC5!A1" display="#X2_DC_8pin_PC5"/>
     <hyperlink ref="H158" location="X3_DO_4pin_BCZ!A1" display="#X3_DO_4pin_BCZ"/>
-    <hyperlink ref="H165" location="X3_24V_BLF_2_5!A1" display="#X3_24V_BLF_2_5"/>
-    <hyperlink ref="H166" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
-    <hyperlink ref="H167" location="S1_SWITCH_CAN!A1" display="#S1_SWITCH_CAN"/>
-    <hyperlink ref="H168" location="X5_DI_10pin_B2CF!A1" display="#X5_DI_10pin_B2CF"/>
-    <hyperlink ref="H169" location="X10_DO_10pin_B2CF!A1" display="#X10_DO_10pin_B2CF"/>
-    <hyperlink ref="H170" location="X1_24V_5pin_BCZ_TGM!A1" display="#X1_24V_5pin_BCZ_TGM"/>
+    <hyperlink ref="H159" location="X4_ACIN_4pin_TGS560_25!A1" display="#X4_ACIN_4pin_TGS560_25"/>
+    <hyperlink ref="H160" location="X4_TGS560_24V_5pin_BCZ!A1" display="#X4_TGS560_24V_5pin_BCZ"/>
+    <hyperlink ref="H161" location="X1_DC_6pin_TGS560_25!A1" display="#X1_DC_6pin_TGS560_25"/>
+    <hyperlink ref="H162" location="X5_RBR_3pin_TGS560_25!A1" display="#X5_RBR_3pin_TGS560_25"/>
+    <hyperlink ref="H163" location="S1_TGS560_DIP!A1" display="#S1_TGS560_DIP"/>
+    <hyperlink ref="H164" location="X3_DO_4pin_BCZ!A1" display="#X3_DO_4pin_BCZ"/>
+    <hyperlink ref="H165" location="X2_ACIN_7pin_2636!A1" display="#X2_ACIN_7pin_2636"/>
+    <hyperlink ref="H166" location="X6_TGS560_50_DCbus!A1" display="#X6_TGS560_50_DCbus"/>
+    <hyperlink ref="H167" location="X3_DO_4pin_BCZ!A1" display="#X3_DO_4pin_BCZ"/>
+    <hyperlink ref="H168" location="X4_TGS560_24V_5pin_BCZ!A1" display="#X4_TGS560_24V_5pin_BCZ"/>
+    <hyperlink ref="H169" location="S1_TGS560_DIP!A1" display="#S1_TGS560_DIP"/>
+    <hyperlink ref="H170" location="X3_24V_BLF_2_5!A1" display="#X3_24V_BLF_2_5"/>
     <hyperlink ref="H171" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
-    <hyperlink ref="H172" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
-    <hyperlink ref="H173" location="X6_FB1_8pin_B2CF_TGM!A1" display="#X6_FB1_8pin_B2CF_TGM"/>
-    <hyperlink ref="H174" location="X7_FB2_8pin_B2CF_TGM!A1" display="#X7_FB2_8pin_B2CF_TGM"/>
-    <hyperlink ref="H175" location="X5_FBE_12pin_B2CF_TGM!A1" display="#X5_FBE_12pin_B2CF_TGM"/>
+    <hyperlink ref="H172" location="S1_SWITCH_CAN!A1" display="#S1_SWITCH_CAN"/>
+    <hyperlink ref="H173" location="X5_DI_10pin_B2CF!A1" display="#X5_DI_10pin_B2CF"/>
+    <hyperlink ref="H174" location="X10_DO_10pin_B2CF!A1" display="#X10_DO_10pin_B2CF"/>
+    <hyperlink ref="H175" location="X1_24V_5pin_BCZ_TGM!A1" display="#X1_24V_5pin_BCZ_TGM"/>
+    <hyperlink ref="H176" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H177" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H178" location="X6_FB1_8pin_B2CF_TGM!A1" display="#X6_FB1_8pin_B2CF_TGM"/>
+    <hyperlink ref="H179" location="X7_FB2_8pin_B2CF_TGM!A1" display="#X7_FB2_8pin_B2CF_TGM"/>
+    <hyperlink ref="H180" location="X5_FBE_12pin_B2CF_TGM!A1" display="#X5_FBE_12pin_B2CF_TGM"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -7864,16 +8192,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7881,13 +8209,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7895,13 +8223,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7909,13 +8237,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7923,13 +8251,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7937,13 +8265,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7951,13 +8279,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7965,13 +8293,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7979,13 +8307,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8017,16 +8345,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8034,13 +8362,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8048,13 +8376,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8062,13 +8390,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8076,13 +8404,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8090,13 +8418,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8104,13 +8432,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8142,16 +8470,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8159,13 +8487,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8173,13 +8501,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8187,13 +8515,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8201,13 +8529,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8215,13 +8543,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8229,13 +8557,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8267,16 +8595,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8284,13 +8612,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8298,13 +8626,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8312,13 +8640,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8326,13 +8654,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8340,13 +8668,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -8375,16 +8703,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8392,13 +8720,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8406,13 +8734,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8444,16 +8772,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8461,13 +8789,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8475,13 +8803,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8489,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8528,16 +8856,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8545,13 +8873,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8559,13 +8887,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8573,13 +8901,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8587,13 +8915,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -8622,16 +8950,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8639,13 +8967,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8653,13 +8981,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8667,13 +8995,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8705,16 +9033,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8722,13 +9050,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8736,13 +9064,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8750,13 +9078,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8764,13 +9092,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8802,16 +9130,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8819,13 +9147,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8833,13 +9161,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8847,13 +9175,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8861,13 +9189,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8889,7 +9217,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.45"/>
@@ -8903,7 +9231,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -8923,7 +9251,7 @@
         <v>5055700501</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>5</v>
@@ -8934,10 +9262,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>22</v>
@@ -8948,10 +9276,10 @@
         <v>21</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>4</v>
@@ -8962,10 +9290,10 @@
         <v>23</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>8</v>
@@ -8976,10 +9304,10 @@
         <v>25</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>8</v>
@@ -8990,10 +9318,10 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>12</v>
@@ -9004,10 +9332,10 @@
         <v>34</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>5</v>
@@ -9018,10 +9346,10 @@
         <v>35</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>6</v>
@@ -9032,10 +9360,10 @@
         <v>37</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>6</v>
@@ -9046,10 +9374,10 @@
         <v>38</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>2</v>
@@ -9060,10 +9388,10 @@
         <v>44</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>6</v>
@@ -9074,10 +9402,10 @@
         <v>46</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
@@ -9088,10 +9416,10 @@
         <v>48</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>6</v>
@@ -9102,10 +9430,10 @@
         <v>50</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>12</v>
@@ -9116,10 +9444,10 @@
         <v>55</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>2</v>
@@ -9130,10 +9458,10 @@
         <v>56</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>2</v>
@@ -9144,7 +9472,7 @@
         <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>63</v>
@@ -9158,7 +9486,7 @@
         <v>59</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>63</v>
@@ -9172,7 +9500,7 @@
         <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>63</v>
@@ -9186,10 +9514,10 @@
         <v>64</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>8</v>
@@ -9200,10 +9528,10 @@
         <v>66</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>8</v>
@@ -9214,10 +9542,10 @@
         <v>68</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>4</v>
@@ -9225,13 +9553,13 @@
     </row>
     <row r="24" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>4</v>
@@ -9242,10 +9570,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>4</v>
@@ -9253,13 +9581,13 @@
     </row>
     <row r="26" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>10</v>
@@ -9267,13 +9595,13 @@
     </row>
     <row r="27" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>10</v>
@@ -9281,13 +9609,13 @@
     </row>
     <row r="28" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>5</v>
@@ -9298,10 +9626,10 @@
         <v>47</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>3</v>
@@ -9309,13 +9637,13 @@
     </row>
     <row r="30" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>8</v>
@@ -9323,13 +9651,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>8</v>
@@ -9337,13 +9665,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>12</v>
@@ -9351,10 +9679,10 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>63</v>
@@ -9368,7 +9696,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>63</v>
@@ -9382,7 +9710,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>63</v>
@@ -9396,7 +9724,7 @@
         <v>39</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>63</v>
@@ -9410,7 +9738,7 @@
         <v>40</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>63</v>
@@ -9424,7 +9752,7 @@
         <v>41</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>63</v>
@@ -9438,10 +9766,10 @@
         <v>43</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>6</v>
@@ -9452,10 +9780,10 @@
         <v>51</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>6</v>
@@ -9466,10 +9794,10 @@
         <v>52</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>6</v>
@@ -9480,13 +9808,125 @@
         <v>54</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9531,6 +9971,14 @@
     <hyperlink ref="A40" location="X3_M1_6pin_BLZ__7_62!A1" display="#X3_M1_6pin_BLZ__7_62"/>
     <hyperlink ref="A41" location="X4_M2_6pin_BLZ__7_62!A1" display="#X4_M2_6pin_BLZ__7_62"/>
     <hyperlink ref="A42" location="X2_560_DC_3pin_BLZ__7_62!A1" display="#X2_560_DC_3pin_BLZ__7_62"/>
+    <hyperlink ref="A43" location="X4_ACIN_4pin_TGS560_25!A1" display="#X4_ACIN_4pin_TGS560_25"/>
+    <hyperlink ref="A44" location="X1_DC_6pin_TGS560_25!A1" display="#X1_DC_6pin_TGS560_25"/>
+    <hyperlink ref="A45" location="X5_RBR_3pin_TGS560_25!A1" display="#X5_RBR_3pin_TGS560_25"/>
+    <hyperlink ref="A46" location="S1_TGS560_DIP!A1" display="#S1_TGS560_DIP"/>
+    <hyperlink ref="A47" location="X4_TGS560_24V_5pin_BCZ!A1" display="#X4_TGS560_24V_5pin_BCZ"/>
+    <hyperlink ref="A48" location="X2_ACIN_7pin_2636!A1" display="#X2_ACIN_7pin_2636"/>
+    <hyperlink ref="A49" location="X6_TGS560_50_DCbus!A1" display="#X6_TGS560_50_DCbus"/>
+    <hyperlink ref="A50" location="XBR_BR_6pin_BLF!A1" display="#XBR_BR_6pin_BLF"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -9557,16 +10005,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9574,13 +10022,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9588,13 +10036,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9602,13 +10050,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9616,13 +10064,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9630,13 +10078,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9644,13 +10092,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9683,16 +10131,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9700,13 +10148,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9714,13 +10162,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9728,13 +10176,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9742,13 +10190,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9756,13 +10204,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -9792,16 +10240,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9809,13 +10257,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9823,13 +10271,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9837,13 +10285,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9851,13 +10299,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -9887,16 +10335,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9904,13 +10352,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9918,13 +10366,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9932,13 +10380,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9946,13 +10394,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -9982,16 +10430,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9999,13 +10447,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10013,13 +10461,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -10048,16 +10496,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10065,13 +10513,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10079,13 +10527,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10093,13 +10541,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10107,13 +10555,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10121,13 +10569,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10135,13 +10583,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10173,16 +10621,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10190,13 +10638,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10204,13 +10652,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10218,13 +10666,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10232,13 +10680,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10246,13 +10694,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10260,13 +10708,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10274,13 +10722,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10288,13 +10736,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10302,13 +10750,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10316,13 +10764,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10352,16 +10800,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10369,10 +10817,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>10</v>
@@ -10383,10 +10831,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>10</v>
@@ -10397,10 +10845,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>10</v>
@@ -10432,16 +10880,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10449,13 +10897,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10463,13 +10911,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10477,13 +10925,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10491,13 +10939,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10505,13 +10953,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10519,13 +10967,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10557,16 +11005,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10574,13 +11022,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10588,13 +11036,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10602,13 +11050,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10616,13 +11064,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10630,13 +11078,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10644,13 +11092,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10658,13 +11106,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10672,13 +11120,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10686,13 +11134,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10700,13 +11148,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10714,13 +11162,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10728,13 +11176,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -10763,16 +11211,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10780,10 +11228,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>16</v>
@@ -10794,10 +11242,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>16</v>
@@ -10808,10 +11256,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>16</v>
@@ -10822,10 +11270,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>16</v>
@@ -10836,10 +11284,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>16</v>
@@ -10871,16 +11319,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10888,13 +11336,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10902,13 +11350,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10967,16 +11415,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10984,13 +11432,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10998,13 +11446,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11012,13 +11460,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11026,13 +11474,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11064,16 +11512,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11081,13 +11529,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11095,13 +11543,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11109,13 +11557,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11123,13 +11571,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11161,16 +11609,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11178,13 +11626,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11192,13 +11640,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11206,13 +11654,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11220,13 +11668,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11258,16 +11706,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11275,13 +11723,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11289,13 +11737,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11303,13 +11751,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11317,13 +11765,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11353,16 +11801,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11370,10 +11818,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>10</v>
@@ -11384,10 +11832,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>10</v>
@@ -11398,10 +11846,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>10</v>
@@ -11433,16 +11881,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11450,10 +11898,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>10</v>
@@ -11464,10 +11912,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>10</v>
@@ -11478,10 +11926,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>10</v>
@@ -11492,10 +11940,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>10</v>
@@ -11506,10 +11954,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>10</v>
@@ -11520,10 +11968,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>10</v>
@@ -11534,10 +11982,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>10</v>
@@ -11548,10 +11996,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>10</v>
@@ -11596,16 +12044,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11613,13 +12061,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11627,13 +12075,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11641,13 +12089,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11655,13 +12103,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -11691,16 +12139,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11708,13 +12156,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11722,13 +12170,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11736,13 +12184,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11750,13 +12198,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -11785,13 +12233,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11799,10 +12247,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11810,10 +12258,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11821,10 +12269,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11832,10 +12280,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11843,10 +12291,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11854,10 +12302,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11865,10 +12313,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11876,10 +12324,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11887,10 +12335,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11898,10 +12346,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11934,16 +12382,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11951,10 +12399,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>10</v>
@@ -11965,10 +12413,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>10</v>
@@ -12000,13 +12448,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12014,10 +12462,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12025,10 +12473,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12036,10 +12484,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12047,10 +12495,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12058,10 +12506,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12069,10 +12517,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12080,10 +12528,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12091,10 +12539,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12102,10 +12550,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12113,10 +12561,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12154,35 +12602,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12244,16 +12692,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12261,13 +12709,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12275,13 +12723,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12289,13 +12737,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12303,13 +12751,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12317,13 +12765,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -12351,10 +12799,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12362,7 +12810,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12370,7 +12818,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12378,7 +12826,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12386,7 +12834,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12394,7 +12842,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12402,7 +12850,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12410,7 +12858,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12418,7 +12866,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12426,7 +12874,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12434,7 +12882,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12442,7 +12890,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12450,7 +12898,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -12479,13 +12927,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12493,10 +12941,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12504,10 +12952,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12515,10 +12963,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12526,10 +12974,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12537,10 +12985,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12548,10 +12996,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12559,10 +13007,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12570,10 +13018,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12605,13 +13053,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12619,10 +13067,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12630,10 +13078,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12641,10 +13089,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12652,10 +13100,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12663,10 +13111,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12674,10 +13122,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12685,10 +13133,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12696,10 +13144,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12732,19 +13180,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12752,13 +13200,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>63</v>
@@ -12769,13 +13217,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>63</v>
@@ -12786,16 +13234,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12803,16 +13251,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12820,16 +13268,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12837,16 +13285,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12857,7 +13305,7 @@
         <v>63</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>63</v>
@@ -12874,7 +13322,7 @@
         <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>63</v>
@@ -12888,16 +13336,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12905,16 +13353,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12922,16 +13370,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12939,16 +13387,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12981,19 +13429,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13001,16 +13449,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13018,16 +13466,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13035,16 +13483,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13052,16 +13500,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13069,16 +13517,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13086,16 +13534,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13106,7 +13554,7 @@
         <v>63</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>63</v>
@@ -13123,7 +13571,7 @@
         <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>63</v>
@@ -13137,16 +13585,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13154,16 +13602,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13196,19 +13644,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13216,16 +13664,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13233,16 +13681,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13250,16 +13698,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13267,16 +13715,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13284,16 +13732,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13301,16 +13749,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13321,7 +13769,7 @@
         <v>63</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>63</v>
@@ -13338,7 +13786,7 @@
         <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>63</v>
@@ -13352,16 +13800,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13369,16 +13817,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13410,13 +13858,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13424,10 +13872,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13435,10 +13883,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13446,10 +13894,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13457,10 +13905,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13468,10 +13916,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13479,10 +13927,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13490,10 +13938,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13501,10 +13949,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13512,10 +13960,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13523,10 +13971,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13534,10 +13982,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13545,10 +13993,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13579,16 +14027,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13596,13 +14044,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13610,13 +14058,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13624,13 +14072,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13638,13 +14086,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13652,13 +14100,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13666,13 +14114,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13680,13 +14128,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13694,13 +14142,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13708,13 +14156,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13722,13 +14170,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13736,13 +14184,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13750,13 +14198,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13764,13 +14212,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13778,13 +14226,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13792,13 +14240,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13806,13 +14254,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13820,13 +14268,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13834,13 +14282,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13848,13 +14296,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13862,13 +14310,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13876,13 +14324,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13890,13 +14338,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -13925,13 +14373,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13939,10 +14387,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13950,10 +14398,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13961,10 +14409,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13972,10 +14420,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13983,10 +14431,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13994,10 +14442,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14005,10 +14453,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14016,10 +14464,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14027,10 +14475,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14038,10 +14486,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14049,10 +14497,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14060,10 +14508,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14071,10 +14519,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14082,10 +14530,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14093,10 +14541,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14104,10 +14552,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14115,10 +14563,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14126,10 +14574,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -14158,13 +14606,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14172,10 +14620,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14183,10 +14631,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14194,10 +14642,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14205,10 +14653,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14216,10 +14664,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14227,10 +14675,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14238,10 +14686,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14249,10 +14697,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -14281,13 +14729,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14295,10 +14743,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14306,10 +14754,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14317,10 +14765,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14328,10 +14776,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14339,10 +14787,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14350,10 +14798,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14361,10 +14809,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14372,10 +14820,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14383,10 +14831,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14394,10 +14842,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14435,13 +14883,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14449,10 +14897,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14460,10 +14908,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14471,10 +14919,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14482,10 +14930,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14493,10 +14941,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14504,10 +14952,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14515,10 +14963,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14526,10 +14974,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14573,16 +15021,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14590,13 +15038,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14604,13 +15052,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14618,13 +15066,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14632,13 +15080,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14646,13 +15094,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14660,13 +15108,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14674,13 +15122,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14724,16 +15172,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14741,13 +15189,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14755,13 +15203,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14821,16 +15269,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14838,13 +15286,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14852,13 +15300,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14866,13 +15314,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14880,13 +15328,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>457</v>
+        <v>196</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14894,13 +15342,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -14927,16 +15375,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14944,13 +15392,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14958,13 +15406,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14972,13 +15420,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -15007,16 +15455,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15024,13 +15472,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15038,13 +15486,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15052,13 +15500,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15066,13 +15514,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15080,13 +15528,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15094,13 +15542,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15132,16 +15580,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15149,13 +15597,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15163,13 +15611,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15177,13 +15625,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15191,13 +15639,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15205,13 +15653,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15219,13 +15667,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15256,16 +15704,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15273,13 +15721,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15287,13 +15735,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15301,13 +15749,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15315,13 +15763,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -15346,70 +15794,70 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15417,7 +15865,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="13"/>
@@ -15427,7 +15875,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="13"/>
@@ -15437,7 +15885,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H10" s="14"/>
       <c r="I10" s="13"/>
@@ -15447,7 +15895,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="13"/>
@@ -15457,7 +15905,7 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H12" s="14"/>
       <c r="I12" s="13"/>
@@ -15467,7 +15915,7 @@
         <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="13"/>
@@ -15477,7 +15925,7 @@
         <v>110</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H14" s="14"/>
       <c r="I14" s="13"/>
@@ -15487,7 +15935,7 @@
         <v>111</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H15" s="14"/>
       <c r="I15" s="13"/>
@@ -15497,7 +15945,7 @@
         <v>1000</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="13"/>
@@ -15507,7 +15955,7 @@
         <v>1001</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="13"/>
@@ -15517,7 +15965,7 @@
         <v>1010</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="C18" s="10"/>
       <c r="H18" s="14"/>
@@ -15528,7 +15976,7 @@
         <v>1011</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="13"/>
@@ -15538,7 +15986,7 @@
         <v>1100</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="13"/>
@@ -15548,7 +15996,7 @@
         <v>1101</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="13"/>
@@ -15558,7 +16006,7 @@
         <v>1110</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="13"/>
@@ -15568,7 +16016,7 @@
         <v>1111</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H23" s="14"/>
       <c r="I23" s="13"/>
@@ -15595,110 +16043,110 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="13"/>
@@ -15710,39 +16158,30 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>489</v>
+        <v>133</v>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>489</v>
+        <v>511</v>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="13"/>
@@ -15805,16 +16244,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15822,13 +16261,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15836,13 +16275,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15850,13 +16289,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15864,13 +16303,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15914,16 +16353,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15931,13 +16370,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15945,13 +16384,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15959,13 +16398,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15973,13 +16412,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15987,13 +16426,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16001,13 +16440,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16045,16 +16484,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16062,13 +16501,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16076,13 +16515,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16090,13 +16529,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16141,26 +16580,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -16189,16 +16628,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16206,13 +16645,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16220,13 +16659,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16234,13 +16673,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16248,13 +16687,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16262,13 +16701,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16276,13 +16715,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16290,13 +16729,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16304,13 +16743,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16318,13 +16757,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16332,13 +16771,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16346,13 +16785,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16360,13 +16799,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16398,16 +16837,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16415,13 +16854,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16429,13 +16868,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16443,13 +16882,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16457,13 +16896,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16471,13 +16910,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16485,13 +16924,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16499,13 +16938,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16513,13 +16952,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
